--- a/InputFields.xlsx
+++ b/InputFields.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="119">
   <si>
     <t xml:space="preserve">Fields</t>
   </si>
@@ -117,6 +117,9 @@
   </si>
   <si>
     <t xml:space="preserve">NdigitNumberGenerator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00</t>
   </si>
   <si>
     <t xml:space="preserve">bankCode</t>
@@ -381,8 +384,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -478,7 +482,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -491,6 +495,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -499,11 +507,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -630,34 +642,34 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F1048576"/>
+  <dimension ref="A1:F79"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="40.94"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="35.84"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="7"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="5" min="4" style="2" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="22.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="3" width="22.29"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="7" style="2" width="11.53"/>
   </cols>
   <sheetData>
-    <row r="1" s="4" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
+    <row r="1" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
     </row>
@@ -677,7 +689,7 @@
       <c r="E2" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="7" t="s">
         <v>8</v>
       </c>
     </row>
@@ -697,7 +709,7 @@
       <c r="E3" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="8" t="s">
         <v>10</v>
       </c>
     </row>
@@ -717,7 +729,7 @@
       <c r="E4" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="3" t="s">
         <v>11</v>
       </c>
     </row>
@@ -737,7 +749,7 @@
       <c r="E5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="3" t="s">
         <v>13</v>
       </c>
     </row>
@@ -757,7 +769,7 @@
       <c r="E6" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="3" t="s">
         <v>10</v>
       </c>
     </row>
@@ -777,12 +789,1076 @@
       <c r="E7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="2"/>
+    </row>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="2"/>
+    </row>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="2"/>
+    </row>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="2"/>
+    </row>
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="2"/>
+    </row>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="2"/>
+    </row>
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" s="2"/>
+    </row>
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" s="2"/>
+    </row>
+    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C21" s="2"/>
+    </row>
+    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C24" s="2"/>
+    </row>
+    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C25" s="2"/>
+    </row>
+    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D26" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D29" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="D30" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="D31" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C32" s="2"/>
+    </row>
+    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C33" s="2"/>
+    </row>
+    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="D34" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D35" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C36" s="2"/>
+    </row>
+    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C37" s="2"/>
+    </row>
+    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C38" s="2"/>
+    </row>
+    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D39" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C40" s="2"/>
+    </row>
+    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D41" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D42" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C43" s="2"/>
+    </row>
+    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C44" s="2"/>
+    </row>
+    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C45" s="2"/>
+    </row>
+    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D46" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D47" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D48" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D49" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D50" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="D51" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C52" s="2"/>
+    </row>
+    <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C53" s="2"/>
+    </row>
+    <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C54" s="2"/>
+    </row>
+    <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D55" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C56" s="2"/>
+    </row>
+    <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="D57" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C58" s="2"/>
+    </row>
+    <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D59" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C60" s="2"/>
+    </row>
+    <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C61" s="2"/>
+    </row>
+    <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C62" s="2"/>
+    </row>
+    <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D63" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C64" s="2"/>
+    </row>
+    <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C65" s="2"/>
+    </row>
+    <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C66" s="2"/>
+    </row>
+    <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D67" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C68" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D68" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D69" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C70" s="2"/>
+    </row>
+    <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="D71" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C72" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="D72" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C73" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D73" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C74" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D74" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D75" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D76" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C77" s="2"/>
+    </row>
+    <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C78" s="2"/>
+    </row>
+    <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C79" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="D79" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -808,13 +1884,13 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
     </row>
@@ -887,7 +1963,7 @@
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>31</v>
@@ -898,7 +1974,7 @@
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>31</v>
@@ -909,7 +1985,7 @@
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>31</v>
@@ -920,18 +1996,18 @@
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>18</v>
@@ -939,18 +2015,18 @@
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>16</v>
@@ -958,10 +2034,10 @@
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C17" s="2" t="n">
         <v>6</v>
@@ -969,26 +2045,26 @@
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C20" s="2" t="n">
         <v>6</v>
@@ -996,10 +2072,10 @@
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C21" s="2" t="n">
         <v>4</v>
@@ -1007,10 +2083,10 @@
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C22" s="2" t="n">
         <v>4</v>
@@ -1018,10 +2094,10 @@
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C23" s="2" t="n">
         <v>6</v>
@@ -1029,10 +2105,10 @@
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C24" s="2" t="n">
         <v>12</v>
@@ -1040,10 +2116,10 @@
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C25" s="2" t="n">
         <v>20</v>
@@ -1051,26 +2127,26 @@
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C28" s="2" t="n">
         <v>20</v>
@@ -1078,7 +2154,7 @@
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>31</v>
@@ -1089,34 +2165,34 @@
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C33" s="2" t="n">
         <v>10</v>
@@ -1124,15 +2200,15 @@
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>31</v>
@@ -1143,7 +2219,7 @@
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>31</v>
@@ -1154,34 +2230,34 @@
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C40" s="2" t="n">
         <v>8</v>
@@ -1189,10 +2265,10 @@
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C41" s="2" t="n">
         <v>4</v>
@@ -1200,10 +2276,10 @@
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C42" s="2" t="n">
         <v>10</v>
@@ -1211,10 +2287,10 @@
     </row>
     <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C43" s="2" t="n">
         <v>5</v>
@@ -1222,7 +2298,7 @@
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>31</v>
@@ -1233,10 +2309,10 @@
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C45" s="2" t="n">
         <v>12</v>
@@ -1244,31 +2320,31 @@
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>31</v>
@@ -1279,18 +2355,18 @@
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C51" s="2" t="n">
         <v>12</v>
@@ -1298,15 +2374,15 @@
     </row>
     <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>31</v>
@@ -1317,23 +2393,23 @@
     </row>
     <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>29</v>
@@ -1341,10 +2417,10 @@
     </row>
     <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C57" s="2" t="n">
         <v>6</v>
@@ -1352,31 +2428,31 @@
     </row>
     <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>31</v>
@@ -1387,7 +2463,7 @@
     </row>
     <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>31</v>
@@ -1398,7 +2474,7 @@
     </row>
     <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>31</v>
@@ -1409,18 +2485,18 @@
     </row>
     <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C65" s="2" t="n">
         <v>32</v>
@@ -1428,10 +2504,10 @@
     </row>
     <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C66" s="2" t="n">
         <v>9</v>
@@ -1439,10 +2515,10 @@
     </row>
     <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C67" s="2" t="n">
         <v>6</v>
@@ -1450,10 +2526,10 @@
     </row>
     <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C68" s="2" t="n">
         <v>6</v>
@@ -1461,7 +2537,7 @@
     </row>
     <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>31</v>
@@ -1472,7 +2548,7 @@
     </row>
     <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>31</v>
@@ -1483,26 +2559,26 @@
     </row>
     <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C73" s="1" t="n">
         <v>17</v>
